--- a/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:15</t>
+    <t xml:space="preserve">2026-09-10 01:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:29</t>
+    <t xml:space="preserve">2026-09-12 22:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
@@ -45,12 +45,12 @@
     <t xml:space="preserve">Hualañé</t>
   </si>
   <si>
+    <t xml:space="preserve">Vichuquén</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pelluhue</t>
   </si>
   <si>
-    <t xml:space="preserve">Vichuquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pelarco</t>
   </si>
   <si>
@@ -69,12 +69,12 @@
     <t xml:space="preserve">Sagrada Familia</t>
   </si>
   <si>
+    <t xml:space="preserve">Retiro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Longaví</t>
   </si>
   <si>
-    <t xml:space="preserve">Retiro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
@@ -96,24 +96,24 @@
     <t xml:space="preserve">Linares</t>
   </si>
   <si>
+    <t xml:space="preserve">Talca</t>
+  </si>
+  <si>
     <t xml:space="preserve">Colbún</t>
   </si>
   <si>
-    <t xml:space="preserve">Talca</t>
+    <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
     <t xml:space="preserve">Romeral</t>
   </si>
   <si>
-    <t xml:space="preserve">San Clemente</t>
+    <t xml:space="preserve">Empedrado</t>
   </si>
   <si>
     <t xml:space="preserve">Molina</t>
   </si>
   <si>
-    <t xml:space="preserve">Empedrado</t>
-  </si>
-  <si>
     <t xml:space="preserve">Yerbas Buenas</t>
   </si>
   <si>
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:40</t>
+    <t xml:space="preserve">2026-09-24 00:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -565,7 +565,7 @@
         <v>2019</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>180.78</v>
+        <v>194.69</v>
       </c>
     </row>
     <row r="3">
@@ -582,7 +582,7 @@
         <v>2019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>144.99</v>
+        <v>157.23</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>2019</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>142.98</v>
+        <v>152.85</v>
       </c>
     </row>
     <row r="5">
@@ -610,13 +610,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7203</v>
+        <v>7309</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>135.42</v>
+        <v>147.1</v>
       </c>
     </row>
     <row r="6">
@@ -627,13 +627,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>7309</v>
+        <v>7203</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>134.51</v>
+        <v>145.1</v>
       </c>
     </row>
     <row r="7">
@@ -650,7 +650,7 @@
         <v>2019</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>124.5</v>
+        <v>132.99</v>
       </c>
     </row>
     <row r="8">
@@ -667,7 +667,7 @@
         <v>2019</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>121.78</v>
+        <v>130.75</v>
       </c>
     </row>
     <row r="9">
@@ -684,7 +684,7 @@
         <v>2019</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>118.94</v>
+        <v>128.69</v>
       </c>
     </row>
     <row r="10">
@@ -701,7 +701,7 @@
         <v>2019</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>118.28</v>
+        <v>127.1</v>
       </c>
     </row>
     <row r="11">
@@ -718,7 +718,7 @@
         <v>2019</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>115.59</v>
+        <v>124.55</v>
       </c>
     </row>
     <row r="12">
@@ -735,7 +735,7 @@
         <v>2019</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>109.83</v>
+        <v>118.63</v>
       </c>
     </row>
     <row r="13">
@@ -746,13 +746,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>7403</v>
+        <v>7405</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>105.72</v>
+        <v>114.4</v>
       </c>
     </row>
     <row r="14">
@@ -763,13 +763,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>7405</v>
+        <v>7403</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>105.54</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="15">
@@ -786,7 +786,7 @@
         <v>2019</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>104.35</v>
+        <v>112.86</v>
       </c>
     </row>
     <row r="16">
@@ -803,7 +803,7 @@
         <v>2019</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>102.42</v>
+        <v>110.03</v>
       </c>
     </row>
     <row r="17">
@@ -820,7 +820,7 @@
         <v>2019</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>102.17</v>
+        <v>109.02</v>
       </c>
     </row>
     <row r="18">
@@ -837,7 +837,7 @@
         <v>2019</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>99.87</v>
+        <v>107.5</v>
       </c>
     </row>
     <row r="19">
@@ -854,7 +854,7 @@
         <v>2019</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>98.24</v>
+        <v>105.72</v>
       </c>
     </row>
     <row r="20">
@@ -871,7 +871,7 @@
         <v>2019</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>97.93</v>
+        <v>105.26</v>
       </c>
     </row>
     <row r="21">
@@ -888,7 +888,7 @@
         <v>2019</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>96.71</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="22">
@@ -899,13 +899,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>7402</v>
+        <v>7101</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>96.39</v>
+        <v>103.57</v>
       </c>
     </row>
     <row r="23">
@@ -916,13 +916,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>7101</v>
+        <v>7402</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>96.04</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="24">
@@ -933,13 +933,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>7306</v>
+        <v>7109</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>94.37</v>
+        <v>100.17</v>
       </c>
     </row>
     <row r="25">
@@ -950,13 +950,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>7109</v>
+        <v>7306</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>93.57</v>
+        <v>99.94</v>
       </c>
     </row>
     <row r="26">
@@ -967,13 +967,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>7304</v>
+        <v>7104</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>93.25</v>
+        <v>99.6</v>
       </c>
     </row>
     <row r="27">
@@ -984,13 +984,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>7104</v>
+        <v>7304</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2019</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>90.78</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="28">
@@ -1007,7 +1007,7 @@
         <v>2019</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>88.26</v>
+        <v>95.03</v>
       </c>
     </row>
     <row r="29">
@@ -1024,7 +1024,7 @@
         <v>2019</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>82.69</v>
+        <v>88.61</v>
       </c>
     </row>
     <row r="30">
@@ -1041,7 +1041,7 @@
         <v>2019</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>78.91</v>
+        <v>84.68</v>
       </c>
     </row>
     <row r="31">
@@ -1058,7 +1058,7 @@
         <v>2019</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>43.79</v>
+        <v>46.53</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:09</t>
+    <t xml:space="preserve">2026-10-02 16:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2019_maule.xlsx
@@ -129,7 +129,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:09</t>
+    <t xml:space="preserve">2026-10-05 16:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
